--- a/output/pdf_financials_xlsx/SMD.xlsx
+++ b/output/pdf_financials_xlsx/SMD.xlsx
@@ -4494,13 +4494,13 @@
         <v>2.661518</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.013044</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.721098</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.808543</v>
       </c>
     </row>
     <row r="93">
@@ -5549,40 +5549,40 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-4.586187</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-2.054309</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-7.223108</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-5.501518</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-5.398876</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-3.675093</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-4.993825</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-7.986265</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-6.611947</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-3.319592</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.352356</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.584048</v>
       </c>
     </row>
     <row r="119">
@@ -7676,7 +7676,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -8596,7 +8600,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12808,7 +12816,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -15100,7 +15112,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E126" s="5" t="n">
         <v>-4.586187</v>
       </c>

--- a/output/pdf_financials_xlsx/SMD.xlsx
+++ b/output/pdf_financials_xlsx/SMD.xlsx
@@ -879,40 +879,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.645034</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.559584</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.30707</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.195924</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.155878</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.12543</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.128926</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.008156</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.10089</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.127269</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.07275</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.042972</v>
       </c>
     </row>
     <row r="13">
@@ -1612,40 +1612,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-41.139923</v>
+        <v>-41.784957</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.792893</v>
+        <v>-4.352477</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-30.352285</v>
+        <v>-30.659355</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.709915</v>
+        <v>2.513991</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-7.108901</v>
+        <v>-7.264779</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-12.232964</v>
+        <v>-12.358394</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.264118</v>
+        <v>-5.393044</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-10.709009</v>
+        <v>-10.717165</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-10.848228</v>
+        <v>-10.949118</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-6.751029</v>
+        <v>-6.878298</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-7.320816</v>
+        <v>-7.393566</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-9.048772</v>
+        <v>-9.091744</v>
       </c>
     </row>
     <row r="28">
@@ -1698,40 +1698,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-41.139923</v>
+        <v>-41.784957</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.792893</v>
+        <v>-4.352477</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-30.352285</v>
+        <v>-30.659355</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.709915</v>
+        <v>2.513991</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.108901</v>
+        <v>-7.264779</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-12.232964</v>
+        <v>-12.358394</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.264118</v>
+        <v>-5.393044</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-10.705496</v>
+        <v>-10.713652</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-10.846111</v>
+        <v>-10.947001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.751029</v>
+        <v>-6.878298</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.320816</v>
+        <v>-7.393566</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-9.048772</v>
+        <v>-9.091744</v>
       </c>
     </row>
     <row r="30">
@@ -9170,7 +9170,11 @@
           <t>Reclamation deposits 8</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -10058,7 +10062,11 @@
           <t>Reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -10724,7 +10732,11 @@
           <t>Reclamation deposit 9</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>0.015114</v>
       </c>
@@ -15620,7 +15632,11 @@
           <t>Change in reclamation deposits</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -17674,7 +17690,11 @@
           <t>Change in reclamation deposit</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E161" s="5" t="n">
         <v>0.070155</v>
       </c>
@@ -20596,7 +20616,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">

--- a/output/pdf_financials_xlsx/SMD.xlsx
+++ b/output/pdf_financials_xlsx/SMD.xlsx
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-41.139923</v>
+        <v>-15.072829</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-3.792893</v>
+        <v>-3.249939</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-30.352285</v>
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>22.402339</v>
+        <v>-3.664755</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.024803</v>
+        <v>-0.518151</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-2.953598</v>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-41.784957</v>
+        <v>-15.717863</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.352477</v>
+        <v>-3.809523</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-30.659355</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-41.784957</v>
+        <v>-15.717863</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.352477</v>
+        <v>-3.809523</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-30.659355</v>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-54.45401295476417</v>
+        <v>-24.31365074200736</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0.6539335541498271</v>
+        <v>-15.94340693779175</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-9.731056492122422</v>
@@ -5260,10 +5260,10 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.065</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012491</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -5386,16 +5386,16 @@
         <v>0</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-1.26057</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-0.166</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-0.73415</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.0495</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -5420,25 +5420,25 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>1.615093</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>2.573862</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.07044499999999999</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>1.251679</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>1.153214</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.310119</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.263004</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -5678,13 +5678,13 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.454063</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.545596</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.16608</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -6279,10 +6279,10 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.065</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012491</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -6326,7 +6326,7 @@
         <v>7.443289</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2.042643</v>
+        <v>-2.107643</v>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
@@ -11800,7 +11800,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -14768,7 +14772,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -15782,7 +15790,11 @@
           <t>Proceeds from sale of marketable securities 5</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -15856,7 +15868,11 @@
           <t>Purchase of marketable securities 5</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -16082,7 +16098,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -17036,7 +17056,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="n">
         <v>1.615093</v>
       </c>
@@ -17102,7 +17126,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -18288,7 +18316,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -18362,7 +18394,11 @@
           <t>Company share repurchases</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E170" s="5" t="n">
         <v>-0.454063</v>
       </c>
@@ -19478,7 +19514,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E185" s="5" t="n">
         <v>-3.523912</v>
       </c>
@@ -23702,7 +23742,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -27286,7 +27330,11 @@
           <t>Income tax recovery 14</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E293" s="5" t="n">
         <v>3.664755</v>
       </c>
